--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-04-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-04-2026.xlsx
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£13.00</t>
+          <t>£14.50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>£13.98</t>
+          <t>£15.38</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£14.06</t>
+          <t>£17.00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>£15.99</t>
+          <t>£17.59</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -717,12 +717,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£18.33</t>
+          <t>£21.15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>£20.19</t>
+          <t>£22.21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,17 +809,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£18.44</t>
+          <t>£21.90</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>£20.98</t>
+          <t>£23.08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>£28.79</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£23.65</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>£26.16</t>
+          <t>£28.78</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>POA</t>
+          <t>£32.41</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£26.51</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>£29.18</t>
+          <t>£32.10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£26.50</t>
+          <t>£31.00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>£29.27</t>
+          <t>£32.20</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£29.74</t>
+          <t>£34.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>£33.70</t>
+          <t>£37.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1269,17 +1269,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£32.52</t>
+          <t>£37.75</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>£36.62</t>
+          <t>£40.28</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£32.50</t>
+          <t>£36.95</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>£36.04</t>
+          <t>£39.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£38.76</t>
+          <t>£47.40</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£38.76</t>
+          <t>£47.40</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£58.88</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£40.15</t>
+          <t>£47.32</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>£43.83</t>
+          <t>£48.21</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£47.85</t>
+          <t>£57.20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>£53.92</t>
+          <t>£59.31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£57.23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>£54.48</t>
+          <t>£59.93</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£48.52</t>
+          <t>£56.28</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>£53.80</t>
+          <t>£59.18</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£33.21</t>
+          <t>£40.40</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£33.21</t>
+          <t>£40.40</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£40.14</t>
+          <t>£50.00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£40.14</t>
+          <t>£50.00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£44.41</t>
+          <t>£53.22</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£44.41</t>
+          <t>£53.22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>£574.55</t>
+          <t>£632.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>£609.5</t>
+          <t>£670.45</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>£571.30</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>£658.68</t>
+          <t>£724.56</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
